--- a/code/statistic_pattern.xlsx
+++ b/code/statistic_pattern.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
-  <si>
-    <t xml:space="preserve">Город</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ФИО</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+  <si>
+    <t xml:space="preserve">Название компании</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ФИО контактного лица</t>
   </si>
   <si>
     <t xml:space="preserve">Должность</t>
@@ -37,7 +37,13 @@
     <t xml:space="preserve">Почта</t>
   </si>
   <si>
+    <t xml:space="preserve">Город контакта</t>
+  </si>
+  <si>
     <t xml:space="preserve">Дата проведения и название мероприятия</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Автор котакта</t>
   </si>
   <si>
     <t xml:space="preserve">Описание</t>
@@ -409,15 +415,17 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28.9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="31.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="32.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="55.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="25.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="31.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="27.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="31.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="32.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="55.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="25.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="25.36"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -442,6 +450,15 @@
       <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C3" s="0"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/code/statistic_pattern.xlsx
+++ b/code/statistic_pattern.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t xml:space="preserve">Название компании</t>
   </si>
@@ -47,6 +47,27 @@
   </si>
   <si>
     <t xml:space="preserve">Описание</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кто клиент</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Интересующая его продукция</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Какие производители его заинтересовали</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дата и время создания</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дата и время последнего обновления</t>
+  </si>
+  <si>
+    <t xml:space="preserve">статус подьверждение администратором выставки</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ФИО подтвердившего администратора</t>
   </si>
 </sst>
 </file>
@@ -149,8 +170,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -158,11 +183,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -415,17 +440,20 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:P3"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="31.62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="27.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="31.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="32.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="55.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="25.36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="25.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="23.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="31.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="27.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="31.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="2" width="32.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="55.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="25.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="25.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="17.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="27.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="40.93"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -456,9 +484,30 @@
       <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C3" s="0"/>
+      <c r="C3" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
